--- a/data/research-experience_es.xlsx
+++ b/data/research-experience_es.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4108B313-BEB7-4B28-97BA-C30BEFC9CE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50689A0F-8FAD-40FB-8174-0CAC8C1D43CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiencia en Investigación" sheetId="1" r:id="rId1"/>
@@ -103,9 +103,6 @@
     <t>Oct. 2023 - Actualmente</t>
   </si>
   <si>
-    <t>Dic. 2023 - Actualmente</t>
-  </si>
-  <si>
     <t>Ene. 2021 - Ene. 2023</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>Investigadora en el Grupo de Investigación Psicología \&amp; Neurociencias (2014 - 2015)</t>
+  </si>
+  <si>
+    <t>Dic. 2023 - Dic. 2024</t>
   </si>
 </sst>
 </file>
@@ -443,17 +443,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="30.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="30.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="122.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="30.5703125" style="2"/>
+    <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="122.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="98.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="30.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -470,7 +470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -487,22 +487,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -514,7 +514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -522,7 +522,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>20</v>
@@ -531,12 +531,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -545,7 +545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -562,12 +562,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
@@ -576,15 +576,15 @@
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
